--- a/DBScripts/Application status tracker.xlsx
+++ b/DBScripts/Application status tracker.xlsx
@@ -1,25 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5056D272-E120-4602-A5FD-4EAFBC3ADD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="45">
   <si>
     <t>User</t>
   </si>
@@ -113,12 +126,54 @@
   </si>
   <si>
     <t>need to work on sp to get next balance for null balance</t>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>FC</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>in app</t>
+  </si>
+  <si>
+    <t>Need to add</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>IRC</t>
+  </si>
+  <si>
+    <t>I1C</t>
+  </si>
+  <si>
+    <t>I2C</t>
+  </si>
+  <si>
+    <t>I5C</t>
+  </si>
+  <si>
+    <t>I10C</t>
+  </si>
+  <si>
+    <t>I20C</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>IN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -229,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -239,12 +294,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -261,6 +314,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -542,7 +608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:I28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -556,19 +622,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="3"/>
@@ -580,7 +646,7 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="10"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
@@ -790,19 +856,19 @@
       <c r="I13" s="1"/>
     </row>
     <row r="15" spans="2:9" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="8"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="3"/>
@@ -814,7 +880,7 @@
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="10"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
@@ -830,7 +896,7 @@
       <c r="G17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -857,13 +923,13 @@
       <c r="D19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -877,19 +943,19 @@
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H20" s="1" t="s">
@@ -909,13 +975,13 @@
       <c r="D21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H21" s="1" t="s">
@@ -944,7 +1010,7 @@
       <c r="G22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I22" s="1"/>
@@ -1005,7 +1071,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="6"/>
+      <c r="I26" s="1"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
@@ -1041,4 +1107,186 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86C8735-F9B6-47B3-A67A-7E4F0FBE26FA}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="17">
+        <v>72</v>
+      </c>
+      <c r="C2" s="17">
+        <v>62</v>
+      </c>
+      <c r="D2" s="17">
+        <f>B2-C2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="17">
+        <v>32</v>
+      </c>
+      <c r="C3" s="17">
+        <v>32</v>
+      </c>
+      <c r="D3" s="17">
+        <f t="shared" ref="D3:D10" si="0">B3-C3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="17">
+        <v>64</v>
+      </c>
+      <c r="C4" s="17">
+        <v>48</v>
+      </c>
+      <c r="D4" s="17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="17">
+        <v>31</v>
+      </c>
+      <c r="C5" s="17">
+        <v>30</v>
+      </c>
+      <c r="D5" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="17">
+        <v>24</v>
+      </c>
+      <c r="C6" s="17">
+        <v>22</v>
+      </c>
+      <c r="D6" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="17">
+        <v>53</v>
+      </c>
+      <c r="C7" s="17">
+        <v>50</v>
+      </c>
+      <c r="D7" s="17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="17">
+        <v>18</v>
+      </c>
+      <c r="C8" s="17">
+        <v>13</v>
+      </c>
+      <c r="D8" s="17">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="17">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
+      <c r="D9" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="17">
+        <v>33</v>
+      </c>
+      <c r="C10" s="17">
+        <v>33</v>
+      </c>
+      <c r="D10" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="4">
+        <f>SUM(B2:B10)</f>
+        <v>329</v>
+      </c>
+      <c r="C11" s="4">
+        <f t="shared" ref="C11:D11" si="1">SUM(C2:C10)</f>
+        <v>290</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DBScripts/Application status tracker.xlsx
+++ b/DBScripts/Application status tracker.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5056D272-E120-4602-A5FD-4EAFBC3ADD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FA4A0A-9FD0-44AF-B9B0-23081F9FC828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="51">
   <si>
     <t>User</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>Update Existing with request</t>
-  </si>
-  <si>
-    <t>Delete using userid</t>
   </si>
   <si>
     <t>Done</t>
@@ -168,6 +165,27 @@
   </si>
   <si>
     <t>IN</t>
+  </si>
+  <si>
+    <t>Need to check deletion with Document</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Filters</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Category wise is not working</t>
   </si>
 </sst>
 </file>
@@ -206,7 +224,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,6 +234,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -284,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -298,24 +334,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -329,6 +347,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,462 +664,516 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I28"/>
+  <dimension ref="B1:J30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="2:10" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="B1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="8"/>
-      <c r="C3" s="4" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
+      <c r="I3" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="J7" s="20"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+      <c r="C9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="20"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="17" spans="2:10" ht="46.2" x14ac:dyDescent="0.85">
+      <c r="B17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="13"/>
+      <c r="C19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="2"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="15" spans="2:9" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="B15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="8"/>
-      <c r="C17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1072,22 +1181,26 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -1096,13 +1209,40 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B17:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1114,164 +1254,164 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="17">
+      <c r="B2" s="11">
         <v>72</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="11">
         <v>62</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="11">
         <f>B2-C2</f>
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="A3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="11">
         <v>32</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="11">
         <v>32</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="11">
         <f t="shared" ref="D3:D10" si="0">B3-C3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11">
+        <v>64</v>
+      </c>
+      <c r="C4" s="11">
+        <v>48</v>
+      </c>
+      <c r="D4" s="11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="17">
-        <v>64</v>
-      </c>
-      <c r="C4" s="17">
-        <v>48</v>
-      </c>
-      <c r="D4" s="17">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="17">
+      <c r="B5" s="11">
         <v>31</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="11">
         <v>30</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="17">
+      <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="11">
         <v>24</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="11">
         <v>22</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="17">
+      <c r="A7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="11">
         <v>53</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="11">
         <v>50</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="17">
+      <c r="A8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="11">
         <v>18</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="11">
         <v>13</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="17">
+      <c r="A9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="11">
         <v>2</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="11">
         <v>0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="17">
+      <c r="A10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="11">
         <v>33</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="11">
         <v>33</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>43</v>
+    <row r="11" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B11" s="4">
         <f>SUM(B2:B10)</f>

--- a/DBScripts/Application status tracker.xlsx
+++ b/DBScripts/Application status tracker.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FA4A0A-9FD0-44AF-B9B0-23081F9FC828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EA4F6B-EA8A-4A51-BE9A-0EAE468E0D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="66">
   <si>
     <t>User</t>
   </si>
@@ -186,6 +187,51 @@
   </si>
   <si>
     <t>Category wise is not working</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Coin/Note</t>
+  </si>
+  <si>
+    <t>Occasion</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Permissions</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>Change Password</t>
+  </si>
+  <si>
+    <t>Need to add Active/Inactive option</t>
+  </si>
+  <si>
+    <t>Deactivate</t>
+  </si>
+  <si>
+    <t>Need to add UpdateAll option &amp; check all option</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Credentials</t>
   </si>
 </sst>
 </file>
@@ -224,7 +270,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,6 +298,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,13 +399,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -365,25 +436,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,325 +729,325 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="23"/>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="20"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18" t="s">
+      <c r="C5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="20"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="27" t="s">
+      <c r="C6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18" t="s">
+      <c r="C7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="20"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26" t="s">
+      <c r="C8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="20"/>
+      <c r="C9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
+      <c r="C10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="20"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="27" t="s">
+      <c r="C11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="20"/>
+      <c r="C12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="20"/>
+      <c r="C13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19" t="s">
+      <c r="C14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="20"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
+      <c r="C15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="12"/>
     </row>
     <row r="17" spans="2:10" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="17"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="24" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="3"/>
@@ -1008,7 +1060,7 @@
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="13"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1429,4 +1481,392 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19436D51-7710-4C0E-A35D-07BDC3915855}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A1" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="23"/>
+      <c r="B3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DBScripts/Application status tracker.xlsx
+++ b/DBScripts/Application status tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EA4F6B-EA8A-4A51-BE9A-0EAE468E0D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0877D2C8-6354-465A-BDCD-094DCDE21993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="66">
   <si>
     <t>User</t>
   </si>
@@ -1485,21 +1485,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19436D51-7710-4C0E-A35D-07BDC3915855}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:8" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="21" t="s">
         <v>9</v>
       </c>
@@ -1510,9 +1509,8 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
@@ -1523,9 +1521,8 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>11</v>
@@ -1534,25 +1531,22 @@
         <v>48</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1561,9 +1555,8 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>52</v>
       </c>
@@ -1574,9 +1567,8 @@
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
@@ -1589,15 +1581,14 @@
       <c r="D6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>1</v>
       </c>
@@ -1610,15 +1601,12 @@
       <c r="D7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="E7" s="19"/>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>54</v>
       </c>
@@ -1631,19 +1619,16 @@
       <c r="D8" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E8" s="20"/>
+      <c r="F8" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
@@ -1654,23 +1639,20 @@
         <v>16</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="G9" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="H9" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>56</v>
       </c>
@@ -1681,23 +1663,20 @@
         <v>16</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="G10" s="19" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>45</v>
       </c>
@@ -1708,19 +1687,16 @@
         <v>16</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20" t="s">
+      <c r="E11" s="20"/>
+      <c r="F11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G11" s="20"/>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>46</v>
       </c>
@@ -1731,17 +1707,14 @@
         <v>16</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="19" t="s">
         <v>47</v>
       </c>
+      <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>57</v>
       </c>
@@ -1751,10 +1724,9 @@
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>58</v>
       </c>
@@ -1771,44 +1743,38 @@
         <v>4</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>63</v>
       </c>
@@ -1819,7 +1785,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>47</v>
@@ -1830,41 +1796,35 @@
       <c r="G16" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="19"/>
+      <c r="B17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DBScripts/Application status tracker.xlsx
+++ b/DBScripts/Application status tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0877D2C8-6354-465A-BDCD-094DCDE21993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECA1E73-E8E7-4C45-9C52-8D29D3368D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="65">
   <si>
     <t>User</t>
   </si>
@@ -216,15 +216,9 @@
     <t>Need to add Active/Inactive option</t>
   </si>
   <si>
-    <t>Deactivate</t>
-  </si>
-  <si>
     <t>Need to add UpdateAll option &amp; check all option</t>
   </si>
   <si>
-    <t>Na</t>
-  </si>
-  <si>
     <t>Routine</t>
   </si>
   <si>
@@ -232,6 +226,9 @@
   </si>
   <si>
     <t>Credentials</t>
+  </si>
+  <si>
+    <t>Needs to check with image add/update like document</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1492,7 @@
     <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.6" x14ac:dyDescent="0.65">
@@ -1572,35 +1569,23 @@
       <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="20"/>
-      <c r="F6" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="F6" s="20"/>
       <c r="G6" s="20"/>
-      <c r="H6" s="19"/>
+      <c r="H6" s="19" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
@@ -1610,44 +1595,26 @@
       <c r="A8" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="19" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>47</v>
-      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="20"/>
-      <c r="F9" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>60</v>
-      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="19" t="s">
         <v>59</v>
       </c>
@@ -1656,43 +1623,25 @@
       <c r="A10" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="19"/>
-      <c r="F10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>4</v>
-      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
       <c r="H10" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>47</v>
-      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="20"/>
-      <c r="F11" s="20" t="s">
-        <v>47</v>
-      </c>
+      <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="H11" s="19"/>
     </row>
@@ -1700,15 +1649,9 @@
       <c r="A12" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>47</v>
-      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
@@ -1730,29 +1673,17 @@
       <c r="A14" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>4</v>
-      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>16</v>
@@ -1775,32 +1706,32 @@
       <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>47</v>
+      <c r="A16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>16</v>
